--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_atacama.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.3492123367642</v>
+      </c>
+      <c r="C2">
         <v>22.56111799680264</v>
-      </c>
-      <c r="C2">
-        <v>29.3492123367642</v>
       </c>
       <c r="D2">
         <v>4.432404458598726</v>
       </c>
       <c r="E2">
-        <v>14.85160222301053</v>
+        <v>19.32008986638288</v>
       </c>
       <c r="F2">
         <v>65.82830791060661</v>
       </c>
       <c r="G2">
-        <v>19.32008986638288</v>
+        <v>14.85160222301053</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.29347401328644</v>
+      </c>
+      <c r="C3">
         <v>27.6357952325127</v>
-      </c>
-      <c r="C3">
-        <v>31.29347401328644</v>
       </c>
       <c r="D3">
         <v>3.618495475113122</v>
       </c>
       <c r="E3">
-        <v>17.38873862798131</v>
+        <v>19.69018932874354</v>
       </c>
       <c r="F3">
         <v>62.92107204327515</v>
       </c>
       <c r="G3">
-        <v>19.69018932874354</v>
+        <v>17.38873862798131</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>37.12007972097658</v>
+      </c>
+      <c r="C4">
         <v>21.0762331838565</v>
-      </c>
-      <c r="C4">
-        <v>37.12007972097658</v>
       </c>
       <c r="D4">
         <v>4.74468085106383</v>
       </c>
       <c r="E4">
+        <v>23.46456692913386</v>
+      </c>
+      <c r="F4">
+        <v>63.21259842519686</v>
+      </c>
+      <c r="G4">
         <v>13.32283464566929</v>
-      </c>
-      <c r="F4">
-        <v>63.21259842519684</v>
-      </c>
-      <c r="G4">
-        <v>23.46456692913386</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.90099349092155</v>
+      </c>
+      <c r="C5">
         <v>29.83898595409386</v>
-      </c>
-      <c r="C5">
-        <v>30.90099349092155</v>
       </c>
       <c r="D5">
         <v>3.351320321469575</v>
       </c>
       <c r="E5">
-        <v>18.56351236146633</v>
+        <v>19.22421142369992</v>
       </c>
       <c r="F5">
         <v>62.21227621483377</v>
       </c>
       <c r="G5">
-        <v>19.22421142369992</v>
+        <v>18.56351236146633</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.13536626533138</v>
+      </c>
+      <c r="C6">
         <v>21.672105322381</v>
-      </c>
-      <c r="C6">
-        <v>31.13536626533138</v>
       </c>
       <c r="D6">
         <v>4.614226375908619</v>
       </c>
       <c r="E6">
+        <v>20.37555228276878</v>
+      </c>
+      <c r="F6">
+        <v>65.44182621502209</v>
+      </c>
+      <c r="G6">
         <v>14.18262150220913</v>
-      </c>
-      <c r="F6">
-        <v>65.4418262150221</v>
-      </c>
-      <c r="G6">
-        <v>20.37555228276878</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.97267200727231</v>
+      </c>
+      <c r="C7">
         <v>29.65172433384467</v>
-      </c>
-      <c r="C7">
-        <v>30.97267200727231</v>
       </c>
       <c r="D7">
         <v>3.372485150411956</v>
       </c>
       <c r="E7">
-        <v>18.46028686132678</v>
+        <v>19.28266982650372</v>
       </c>
       <c r="F7">
         <v>62.2570433121695</v>
       </c>
       <c r="G7">
-        <v>19.28266982650372</v>
+        <v>18.46028686132678</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>34.22238918106687</v>
+      </c>
+      <c r="C8">
         <v>39.36889556724267</v>
-      </c>
-      <c r="C8">
-        <v>34.22238918106687</v>
       </c>
       <c r="D8">
         <v>2.540076335877862</v>
       </c>
       <c r="E8">
-        <v>22.67907379355118</v>
+        <v>19.71434754382168</v>
       </c>
       <c r="F8">
         <v>57.60657866262714</v>
       </c>
       <c r="G8">
-        <v>19.71434754382168</v>
+        <v>22.67907379355118</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.93755496921724</v>
+      </c>
+      <c r="C9">
         <v>30.34300791556728</v>
-      </c>
-      <c r="C9">
-        <v>32.93755496921724</v>
       </c>
       <c r="D9">
         <v>3.295652173913044</v>
       </c>
       <c r="E9">
-        <v>18.58335577699973</v>
+        <v>20.17236735793159</v>
       </c>
       <c r="F9">
         <v>61.24427686506868</v>
       </c>
       <c r="G9">
-        <v>20.17236735793159</v>
+        <v>18.58335577699973</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>31.37911781127862</v>
+      </c>
+      <c r="C10">
         <v>32.70519262981574</v>
-      </c>
-      <c r="C10">
-        <v>31.37911781127862</v>
       </c>
       <c r="D10">
         <v>3.057618437900128</v>
       </c>
       <c r="E10">
-        <v>19.93194385367928</v>
+        <v>19.12377711612081</v>
       </c>
       <c r="F10">
-        <v>60.94427903019991</v>
+        <v>60.94427903019992</v>
       </c>
       <c r="G10">
-        <v>19.1237771161208</v>
+        <v>19.93194385367929</v>
       </c>
     </row>
   </sheetData>
